--- a/Examples/Powder_Raman/Finite_difference/results.ref.xlsx
+++ b/Examples/Powder_Raman/Finite_difference/results.ref.xlsx
@@ -238,13 +238,13 @@
     <t>Raman electro-optic term</t>
   </si>
   <si>
-    <t>Raman laser frequency</t>
-  </si>
-  <si>
     <t>Raman laser polarisation</t>
   </si>
   <si>
     <t>VV</t>
+  </si>
+  <si>
+    <t>Raman laser wavelength</t>
   </si>
   <si>
     <t>Raman orientation samples</t>
@@ -2043,8 +2043,8 @@
       <c r="B21" t="s">
         <v>72</v>
       </c>
-      <c r="C21">
-        <v>785</v>
+      <c r="C21" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -2052,10 +2052,10 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>73</v>
-      </c>
-      <c r="C22" t="s">
         <v>74</v>
+      </c>
+      <c r="C22">
+        <v>785</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -2348,8 +2348,8 @@
       <c r="B50" t="s">
         <v>72</v>
       </c>
-      <c r="C50">
-        <v>785</v>
+      <c r="C50" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -2357,10 +2357,10 @@
         <v>1</v>
       </c>
       <c r="B51" t="s">
-        <v>73</v>
-      </c>
-      <c r="C51" t="s">
         <v>74</v>
+      </c>
+      <c r="C51">
+        <v>785</v>
       </c>
     </row>
     <row r="52" spans="1:3">

--- a/Examples/Powder_Raman/Finite_difference/results.ref.xlsx
+++ b/Examples/Powder_Raman/Finite_difference/results.ref.xlsx
@@ -130,13 +130,13 @@
     <t>Absorption maximum (L/mole/cm)</t>
   </si>
   <si>
-    <t>Raman R_total (Å4/amu)</t>
+    <t>Raman R_total (Å⁴/amu)</t>
   </si>
   <si>
-    <t>Raman R_parallel (Å4/amu)</t>
+    <t>Raman R_parallel (Å⁴/amu)</t>
   </si>
   <si>
-    <t>Raman R_perp (Å4/amu)</t>
+    <t>Raman R_perp (Å⁴/amu)</t>
   </si>
   <si>
     <t>No</t>
@@ -1148,13 +1148,13 @@
         <v>4.865514602443501E-18</v>
       </c>
       <c r="I26">
-        <v>2.727278544530838E-30</v>
+        <v>7.879820708078788E-31</v>
       </c>
       <c r="J26">
-        <v>1.568317784564591E-30</v>
+        <v>4.531280085212645E-31</v>
       </c>
       <c r="K26">
-        <v>1.158960759966247E-30</v>
+        <v>3.348540622866143E-31</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1180,13 +1180,13 @@
         <v>6.325840725797504E-15</v>
       </c>
       <c r="I27">
-        <v>7.737673179339566E-30</v>
+        <v>2.235616067642786E-30</v>
       </c>
       <c r="J27">
-        <v>4.603463600305887E-30</v>
+        <v>1.330060982561552E-30</v>
       </c>
       <c r="K27">
-        <v>3.134209579033679E-30</v>
+        <v>9.055550850812344E-31</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1212,13 +1212,13 @@
         <v>8.921977583559484E-15</v>
       </c>
       <c r="I28">
-        <v>2.018738424865296E-29</v>
+        <v>5.832663068591835E-30</v>
       </c>
       <c r="J28">
-        <v>1.153346333362675E-29</v>
+        <v>3.332319076627848E-30</v>
       </c>
       <c r="K28">
-        <v>8.65392091502621E-30</v>
+        <v>2.500343991963986E-30</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1244,13 +1244,13 @@
         <v>1.67305599474281E-07</v>
       </c>
       <c r="I29">
-        <v>3.588779008731042</v>
+        <v>1.036892077137725</v>
       </c>
       <c r="J29">
-        <v>2.050730844526949</v>
+        <v>0.5925097532778478</v>
       </c>
       <c r="K29">
-        <v>1.538048164204093</v>
+        <v>0.4443823238598773</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1276,13 +1276,13 @@
         <v>8.450566867474409E-06</v>
       </c>
       <c r="I30">
-        <v>3.594578254884464</v>
+        <v>1.038567630961247</v>
       </c>
       <c r="J30">
-        <v>2.054047641212325</v>
+        <v>0.5934680625513297</v>
       </c>
       <c r="K30">
-        <v>1.540530613672139</v>
+        <v>0.4450995684099177</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1308,13 +1308,13 @@
         <v>0.0003571182824793941</v>
       </c>
       <c r="I31">
-        <v>8.348947734390006E-07</v>
+        <v>2.412229267158742E-07</v>
       </c>
       <c r="J31">
-        <v>4.780367571980992E-07</v>
+        <v>1.38117316478226E-07</v>
       </c>
       <c r="K31">
-        <v>3.568580162409014E-07</v>
+        <v>1.031056102376482E-07</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1340,13 +1340,13 @@
         <v>8758.127840988529</v>
       </c>
       <c r="I32">
-        <v>22.52234148432835</v>
+        <v>6.507293256808216</v>
       </c>
       <c r="J32">
-        <v>20.24516636287772</v>
+        <v>5.849357831990239</v>
       </c>
       <c r="K32">
-        <v>2.277175121450632</v>
+        <v>0.6579354248179772</v>
       </c>
     </row>
     <row r="33" spans="2:11">
@@ -1372,13 +1372,13 @@
         <v>8295.623782319928</v>
       </c>
       <c r="I33">
-        <v>0.6251505443801689</v>
+        <v>0.1806223355935575</v>
       </c>
       <c r="J33">
-        <v>0.3571021118101702</v>
+        <v>0.1031761358290049</v>
       </c>
       <c r="K33">
-        <v>0.2680484325699987</v>
+        <v>0.07744619976455264</v>
       </c>
     </row>
     <row r="34" spans="2:11">
@@ -1404,13 +1404,13 @@
         <v>8295.30198498784</v>
       </c>
       <c r="I34">
-        <v>0.6258222400399263</v>
+        <v>0.1808164060298134</v>
       </c>
       <c r="J34">
-        <v>0.3574736770607281</v>
+        <v>0.1032834907437282</v>
       </c>
       <c r="K34">
-        <v>0.2683485629791981</v>
+        <v>0.07753291528608512</v>
       </c>
     </row>
     <row r="35" spans="2:11">
@@ -1436,13 +1436,13 @@
         <v>0.007148044999887176</v>
       </c>
       <c r="I35">
-        <v>7.658001156345244</v>
+        <v>2.212596737332571</v>
       </c>
       <c r="J35">
-        <v>4.376001840673637</v>
+        <v>1.264341333666849</v>
       </c>
       <c r="K35">
-        <v>3.281999315671607</v>
+        <v>0.9482554036657224</v>
       </c>
     </row>
     <row r="36" spans="2:11">
@@ -1468,13 +1468,13 @@
         <v>7.392352994485575E-07</v>
       </c>
       <c r="I36">
-        <v>7.658384518541916</v>
+        <v>2.212707500693434</v>
       </c>
       <c r="J36">
-        <v>4.376219463411083</v>
+        <v>1.264404210565012</v>
       </c>
       <c r="K36">
-        <v>3.282165055130833</v>
+        <v>0.9483032901284224</v>
       </c>
     </row>
     <row r="37" spans="2:11">
@@ -1500,13 +1500,13 @@
         <v>0.0003881727200935561</v>
       </c>
       <c r="I37">
-        <v>3.170040570999366E-06</v>
+        <v>9.159075953904004E-07</v>
       </c>
       <c r="J37">
-        <v>2.759544735068553E-06</v>
+        <v>7.973046167898345E-07</v>
       </c>
       <c r="K37">
-        <v>4.104958359308128E-07</v>
+        <v>1.186029786005658E-07</v>
       </c>
     </row>
   </sheetData>
